--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488176_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488176_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9413</v>
+        <v>5.6876</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4947</v>
+        <v>3.1917</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4466</v>
+        <v>2.4959</v>
       </c>
       <c r="G2" t="n">
         <v>3.2295</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7318</v>
+        <v>-0.9855</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.532</v>
+        <v>-0.835</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1997</v>
+        <v>-0.1505</v>
       </c>
       <c r="V2" t="n">
         <v>2.5172</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7818</v>
+        <v>4.1982</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0225</v>
+        <v>3.1434</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7593</v>
+        <v>1.0547</v>
       </c>
       <c r="G3" t="n">
         <v>5.0358</v>
@@ -688,13 +688,13 @@
         <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3102</v>
+        <v>-0.8938</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4414</v>
+        <v>-0.3205</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8687</v>
+        <v>-0.5733</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3144</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7369</v>
+        <v>0.9334</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3333</v>
+        <v>-0.2354</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0702</v>
+        <v>1.1687</v>
       </c>
       <c r="G5" t="n">
         <v>0.1278</v>
@@ -844,13 +844,13 @@
         <v>1.1117</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5026</v>
+        <v>-0.3062</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4377</v>
+        <v>-0.3398</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0649</v>
+        <v>0.0336</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2776</v>
+        <v>0.3022</v>
       </c>
       <c r="E6" t="n">
         <v>-0.0547</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3323</v>
+        <v>0.3569</v>
       </c>
       <c r="G6" t="n">
         <v>0.1306</v>
@@ -922,13 +922,13 @@
         <v>0.1853</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0383</v>
+        <v>-0.0137</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0331</v>
+        <v>-0.5759</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4334</v>
+        <v>-0.4593</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4664</v>
+        <v>-0.1166</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.121</v>
+        <v>0.6167</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3451</v>
+        <v>0.188</v>
       </c>
       <c r="I7" t="n">
-        <v>1.224</v>
+        <v>0.4287</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3881</v>
+        <v>1.6806</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7271</v>
+        <v>0.7683</v>
       </c>
       <c r="L7" t="n">
-        <v>1.339</v>
+        <v>0.9124</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.733</v>
+        <v>-1.064</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.618</v>
+        <v>-0.5803</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.115</v>
+        <v>-0.4837</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7793</v>
+        <v>0.9264</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1117</v>
       </c>
       <c r="R7" t="n">
-        <v>3.891</v>
+        <v>2.0382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2636</v>
+        <v>0.0843</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6964</v>
+        <v>-0.3982</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4328</v>
+        <v>0.4825</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8888</v>
+        <v>-2.2033</v>
       </c>
       <c r="W7" t="n">
         <v>-0.63</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2589</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6109</v>
+        <v>-1.2422</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6666</v>
+        <v>-2.5855</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0557</v>
+        <v>1.3433</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6167</v>
+        <v>-1.121</v>
       </c>
       <c r="H8" t="n">
-        <v>0.188</v>
+        <v>-2.3451</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4287</v>
+        <v>1.224</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6806</v>
+        <v>-0.3881</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7683</v>
+        <v>-1.7271</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9124</v>
+        <v>1.339</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.064</v>
+        <v>-0.733</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5803</v>
+        <v>-0.618</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4837</v>
+        <v>-0.115</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9264</v>
+        <v>2.7793</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1117</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0382</v>
+        <v>3.891</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0492</v>
+        <v>-1.0116</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6056</v>
+        <v>-0.4557</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6548</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.2033</v>
+        <v>-1.8888</v>
       </c>
       <c r="W8" t="n">
         <v>-0.63</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5733</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2169</v>
+        <v>-1.7305</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9994</v>
+        <v>-3.193</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7825</v>
+        <v>1.4625</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0868</v>
@@ -1156,13 +1156,13 @@
         <v>3.7057</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4097</v>
+        <v>-0.9233</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5867</v>
+        <v>-0.7803</v>
       </c>
       <c r="U9" t="n">
-        <v>0.177</v>
+        <v>-0.143</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3144</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3771</v>
+        <v>-2.3919</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9748</v>
+        <v>-2.6695</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5977</v>
+        <v>0.2776</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6148</v>
@@ -1234,13 +1234,13 @@
         <v>2.594</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4855</v>
+        <v>-1.5003</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3132</v>
+        <v>-1.0079</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1724</v>
+        <v>-0.4925</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9444</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7128</v>
+        <v>-3.6811</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9368</v>
+        <v>-3.1759</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.776</v>
+        <v>-0.5052</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7193</v>
@@ -1312,13 +1312,13 @@
         <v>2.0382</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1625</v>
+        <v>-1.1307</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.332</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8304</v>
+        <v>-0.5596</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9428</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8281</v>
+        <v>-5.3806</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.7145</v>
+        <v>-6.4639</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8863</v>
+        <v>1.0833</v>
       </c>
       <c r="G12" t="n">
         <v>-5.6506</v>
@@ -1390,13 +1390,13 @@
         <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1781</v>
+        <v>-0.7306</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0396</v>
+        <v>-0.789</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1385</v>
+        <v>0.0584</v>
       </c>
       <c r="V12" t="n">
         <v>0.63</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.031000000000001</v>
+        <v>-2.9367</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.6522</v>
+        <v>-11.558</v>
       </c>
       <c r="F13" t="n">
-        <v>8.621</v>
+        <v>8.621099999999998</v>
       </c>
       <c r="G13" t="n">
         <v>-4.108000000000001</v>
@@ -1450,7 +1450,7 @@
         <v>0.2670000000000008</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.462700000000001</v>
+        <v>-5.4627</v>
       </c>
       <c r="N13" t="n">
         <v>-3.4671</v>
@@ -1468,16 +1468,16 @@
         <v>22.2344</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.5059</v>
+        <v>-7.4114</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.6465</v>
+        <v>-5.5522</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8592</v>
+        <v>-1.8593</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.460900000000001</v>
+        <v>-3.4609</v>
       </c>
       <c r="W13" t="n">
         <v>2.8305</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9715</v>
+        <v>6.0695</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1208</v>
+        <v>3.2187</v>
       </c>
       <c r="F14" t="n">
         <v>2.8507</v>
@@ -1546,10 +1546,10 @@
         <v>1.6676</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5582</v>
+        <v>1.6561</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4726</v>
+        <v>0.5705</v>
       </c>
       <c r="U14" t="n">
         <v>1.0856</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0316</v>
+        <v>2.1788</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.1694</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9602</v>
+        <v>2.0094</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1874</v>
@@ -1624,13 +1624,13 @@
         <v>1.297</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6457</v>
+        <v>1.7929</v>
       </c>
       <c r="T15" t="n">
-        <v>0.725</v>
+        <v>0.8229</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9207</v>
+        <v>0.9699</v>
       </c>
       <c r="V15" t="n">
         <v>1.5733</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8492</v>
+        <v>0.7775</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.001</v>
+        <v>-1.3927</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8502</v>
+        <v>2.1702</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2846</v>
@@ -1780,13 +1780,13 @@
         <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6161</v>
+        <v>1.5445</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1466</v>
+        <v>0.7549</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4695</v>
+        <v>0.7896</v>
       </c>
       <c r="V17" t="n">
         <v>1.2589</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5927</v>
+        <v>0.5838</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.627</v>
+        <v>-0.1317</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2197</v>
+        <v>0.7155</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5447</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1323</v>
+        <v>1.2111</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6943</v>
+        <v>-0.6664</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8057</v>
+        <v>0.8887</v>
       </c>
       <c r="K18" t="n">
         <v>0.7642</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0415</v>
+        <v>0.1244</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2437</v>
+        <v>-0.344</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8966</v>
+        <v>0.4469</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6529</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.2234</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9646</v>
+        <v>-1.1117</v>
       </c>
       <c r="R18" t="n">
         <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9397</v>
+        <v>-0.2192</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2174</v>
+        <v>-0.5375</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7222</v>
+        <v>0.3183</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3144</v>
+        <v>0.6289</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3144</v>
+        <v>0.6289</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>M. MURILLO PONS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4613</v>
+        <v>0.3883</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2296</v>
+        <v>-0.4908</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6909</v>
+        <v>0.8792</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5447</v>
+        <v>-0.3401</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2111</v>
+        <v>-0.2095</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6664</v>
+        <v>-0.1306</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8887</v>
+        <v>-0.6099</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7642</v>
+        <v>0.0429</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1244</v>
+        <v>-0.6529</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.344</v>
+        <v>0.2699</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4469</v>
+        <v>-0.2524</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7907999999999999</v>
+        <v>0.5223</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3417</v>
+        <v>0.5431</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6354</v>
+        <v>0.1191</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2937</v>
+        <v>0.424</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MURILLO PONS</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3643</v>
+        <v>0.2155</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5888</v>
+        <v>-0.9869</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9530999999999999</v>
+        <v>1.2025</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3401</v>
+        <v>0.911</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2095</v>
+        <v>0.1875</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1306</v>
+        <v>0.7235</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6099</v>
+        <v>0.1179</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0429</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6529</v>
+        <v>0.6849</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2699</v>
+        <v>0.793</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2524</v>
+        <v>0.7544</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5223</v>
+        <v>0.0386</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1853</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.297</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>0.519</v>
+        <v>0.6746</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0211</v>
+        <v>0.1921</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4979</v>
+        <v>0.4825</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ AMESTOY</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2818</v>
+        <v>-0.0447</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6686</v>
+        <v>-1.1166</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3868</v>
+        <v>1.072</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7962</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0517</v>
+        <v>-0.1323</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8479</v>
+        <v>0.6943</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0105</v>
+        <v>0.8057</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2751</v>
+        <v>0.7642</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2856</v>
+        <v>0.0415</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2143</v>
+        <v>-0.2437</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2234</v>
+        <v>-0.8966</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4377</v>
+        <v>0.6529</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>-2.9646</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2072</v>
+        <v>1.3023</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4377</v>
+        <v>0.7278</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2305</v>
+        <v>0.5745</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.315</v>
+        <v>0.3144</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.315</v>
+        <v>0.3144</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>A. FERNANDEZ AMESTOY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2982</v>
+        <v>-0.1346</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5745</v>
+        <v>-0.5707</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2764</v>
+        <v>0.4361</v>
       </c>
       <c r="G22" t="n">
-        <v>0.911</v>
+        <v>0.7962</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1875</v>
+        <v>-0.0517</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7235</v>
+        <v>0.8479</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1179</v>
+        <v>1.0105</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.2751</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6849</v>
+        <v>1.2856</v>
       </c>
       <c r="M22" t="n">
-        <v>0.793</v>
+        <v>-0.2143</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7544</v>
+        <v>0.2234</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0386</v>
+        <v>-0.4377</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7411</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.297</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1609</v>
+        <v>-0.06</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3954</v>
+        <v>-0.3398</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5563</v>
+        <v>0.2798</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6289</v>
+        <v>-0.315</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1546</v>
+        <v>-1.0561</v>
       </c>
       <c r="E23" t="n">
         <v>-1.269</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1144</v>
+        <v>0.2129</v>
       </c>
       <c r="G23" t="n">
         <v>-1.132</v>
@@ -2248,13 +2248,13 @@
         <v>0.3706</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3932</v>
+        <v>-0.2947</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3283</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0649</v>
+        <v>0.0336</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3865</v>
+        <v>-2.1475</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2194</v>
+        <v>-4.6111</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8329</v>
+        <v>2.4635</v>
       </c>
       <c r="G24" t="n">
         <v>-0.035</v>
@@ -2326,13 +2326,13 @@
         <v>1.8529</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2632</v>
+        <v>1.5022</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.3507</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5208</v>
+        <v>1.1515</v>
       </c>
       <c r="V24" t="n">
         <v>1.5733</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6847</v>
+        <v>-4.3657</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2017</v>
+        <v>-3.0058</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.483</v>
+        <v>-1.3599</v>
       </c>
       <c r="G25" t="n">
         <v>-1.2439</v>
@@ -2404,13 +2404,13 @@
         <v>0.7411</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2549</v>
+        <v>0.064</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.669</v>
+        <v>-0.4731</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4141</v>
+        <v>0.5372</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8888</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4.031</v>
+        <v>4.030999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.6211</v>
+        <v>-8.620999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>12.6523</v>
+        <v>12.6521</v>
       </c>
       <c r="G26" t="n">
-        <v>4.107800000000001</v>
+        <v>4.1078</v>
       </c>
       <c r="H26" t="n">
         <v>2.3793</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7286</v>
+        <v>1.728600000000001</v>
       </c>
       <c r="J26" t="n">
         <v>5.462599999999999</v>
@@ -2488,7 +2488,7 @@
         <v>1.8593</v>
       </c>
       <c r="U26" t="n">
-        <v>6.646400000000001</v>
+        <v>6.6465</v>
       </c>
       <c r="V26" t="n">
         <v>3.4611</v>
